--- a/markets/network/dist/20261022_AI網通市場模型_v0.2.1.xlsx
+++ b/markets/network/dist/20261022_AI網通市場模型_v0.2.1.xlsx
@@ -270,7 +270,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="401">
   <si>
     <r>
       <rPr>
@@ -299,7 +299,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v0.2</t>
+      <t xml:space="preserve">v0.2.1</t>
     </r>
     <r>
       <rPr>
@@ -404,6 +404,127 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v0.2.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ITU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改讀 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tokenomics </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">快照、不取整（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GB300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">VR200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rubin Ultra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Hopper</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；網通金額不變。</t>
     </r>
   </si>
   <si>
@@ -13938,14 +14059,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Cambria"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -14022,11 +14143,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14322,7 +14443,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="170"/>
@@ -14338,45 +14459,50 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
+    <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+    </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -14410,694 +14536,694 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>5.4</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2.4</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>-0.5</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>1.7</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>7</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0.15</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0.3</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0.15</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0.5</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>0.75</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>1.5</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>0.15</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>3.85</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>5.5</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>7</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>0.15</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2.5</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>3</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>0.15</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>4.5</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>5</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>0.15</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D38" s="7" t="n">
         <v>1194</v>
@@ -15109,21 +15235,21 @@
         <v>1792</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D39" s="7" t="n">
         <v>1194</v>
@@ -15135,21 +15261,21 @@
         <v>1792</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2150</v>
@@ -15161,21 +15287,21 @@
         <v>3226</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D41" s="7" t="n">
         <v>1672</v>
@@ -15187,21 +15313,21 @@
         <v>2508</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>956</v>
@@ -15213,21 +15339,21 @@
         <v>1434</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>2099</v>
@@ -15239,21 +15365,21 @@
         <v>3149</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>2334</v>
@@ -15265,21 +15391,21 @@
         <v>3500</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D45" s="7" t="n">
         <v>2334</v>
@@ -15291,21 +15417,21 @@
         <v>3500</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>4201</v>
@@ -15317,21 +15443,21 @@
         <v>6301</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D47" s="7" t="n">
         <v>3267</v>
@@ -15343,21 +15469,21 @@
         <v>4901</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D48" s="7" t="n">
         <v>1867</v>
@@ -15369,21 +15495,21 @@
         <v>2801</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>5600</v>
@@ -15395,21 +15521,21 @@
         <v>8400</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D50" s="7" t="n">
         <v>3500</v>
@@ -15421,21 +15547,21 @@
         <v>5250</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D51" s="7" t="n">
         <v>3500</v>
@@ -15447,21 +15573,21 @@
         <v>5250</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>4201</v>
@@ -15473,21 +15599,21 @@
         <v>6301</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D53" s="7" t="n">
         <v>3267</v>
@@ -15499,21 +15625,21 @@
         <v>4901</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D54" s="7" t="n">
         <v>1867</v>
@@ -15525,21 +15651,21 @@
         <v>2801</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>5600</v>
@@ -15551,21 +15677,21 @@
         <v>8400</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>240</v>
@@ -15577,21 +15703,21 @@
         <v>360</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D57" s="7" t="n">
         <v>80</v>
@@ -15603,21 +15729,21 @@
         <v>120</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>2016</v>
@@ -15629,21 +15755,21 @@
         <v>3024</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D59" s="7" t="n">
         <v>1568</v>
@@ -15655,21 +15781,21 @@
         <v>2352</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D60" s="7" t="n">
         <v>896</v>
@@ -15681,21 +15807,21 @@
         <v>1344</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>1600</v>
@@ -15707,21 +15833,21 @@
         <v>2400</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B62" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D62" s="7" t="n">
         <v>240</v>
@@ -15733,21 +15859,21 @@
         <v>360</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>80</v>
@@ -15759,21 +15885,21 @@
         <v>120</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>2016</v>
@@ -15785,21 +15911,21 @@
         <v>3024</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>1568</v>
@@ -15811,21 +15937,21 @@
         <v>2352</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>896</v>
@@ -15837,21 +15963,21 @@
         <v>1344</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>1600</v>
@@ -15863,21 +15989,21 @@
         <v>2400</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D68" s="7" t="n">
         <v>1867</v>
@@ -15889,21 +16015,21 @@
         <v>2801</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D69" s="7" t="n">
         <v>1867</v>
@@ -15915,21 +16041,21 @@
         <v>2801</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>3361</v>
@@ -15941,21 +16067,21 @@
         <v>5041</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D71" s="7" t="n">
         <v>2614</v>
@@ -15967,21 +16093,21 @@
         <v>3920</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D72" s="7" t="n">
         <v>1494</v>
@@ -15993,21 +16119,21 @@
         <v>2240</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>4480</v>
@@ -16019,21 +16145,21 @@
         <v>6720</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D74" s="7" t="n">
         <v>640</v>
@@ -16045,21 +16171,21 @@
         <v>960</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D75" s="7" t="n">
         <v>960</v>
@@ -16071,21 +16197,21 @@
         <v>1440</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>640</v>
@@ -16097,21 +16223,21 @@
         <v>960</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B77" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D77" s="7" t="n">
         <v>1200</v>
@@ -16123,21 +16249,21 @@
         <v>1800</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D78" s="7" t="n">
         <v>240</v>
@@ -16149,21 +16275,21 @@
         <v>360</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D79" s="7" t="n">
         <v>320</v>
@@ -16175,21 +16301,21 @@
         <v>480</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D80" s="7" t="n">
         <v>480</v>
@@ -16201,21 +16327,21 @@
         <v>720</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B81" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D81" s="7" t="n">
         <v>640</v>
@@ -16227,21 +16353,21 @@
         <v>960</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>640</v>
@@ -16253,21 +16379,21 @@
         <v>960</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D83" s="7" t="n">
         <v>960</v>
@@ -16279,21 +16405,21 @@
         <v>1440</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D84" s="7" t="n">
         <v>240</v>
@@ -16305,21 +16431,21 @@
         <v>360</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B85" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>240</v>
@@ -16331,21 +16457,21 @@
         <v>360</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D86" s="7" t="n">
         <v>480</v>
@@ -16357,21 +16483,21 @@
         <v>720</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D87" s="7" t="n">
         <v>640</v>
@@ -16383,21 +16509,21 @@
         <v>960</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>640</v>
@@ -16409,21 +16535,21 @@
         <v>960</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D89" s="7" t="n">
         <v>960</v>
@@ -16435,21 +16561,21 @@
         <v>1440</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D90" s="7" t="n">
         <v>240</v>
@@ -16461,21 +16587,21 @@
         <v>360</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D91" s="7" t="n">
         <v>240</v>
@@ -16487,359 +16613,359 @@
         <v>360</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>66.1944444444444</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E94" s="7" t="n">
         <v>128.833333333333</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E95" s="7" t="n">
         <v>257.166666666667</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E96" s="7" t="n">
         <v>38.3125</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>40</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E98" s="7" t="n">
         <v>100</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E99" s="7" t="n">
         <v>25</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E100" s="7" t="n">
         <v>20</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E101" s="7" t="n">
         <v>20</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E103" s="7" t="n">
         <v>0.01</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E104" s="7" t="n">
         <v>0.03</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>0.05</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E106" s="7" t="n">
         <v>0.08</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E108" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B109" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E109" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E110" s="7" t="n">
         <v>0.2</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D111" s="7" t="n">
         <v>0.4</v>
@@ -16851,26 +16977,26 @@
         <v>0.8</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>0.3</v>
@@ -16882,21 +17008,21 @@
         <v>0.7</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D114" s="7" t="n">
         <v>0.35</v>
@@ -16908,21 +17034,21 @@
         <v>0.55</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B115" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D115" s="7" t="n">
         <v>0.1</v>
@@ -16934,18 +17060,18 @@
         <v>0.3</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D116" s="7" t="n">
         <v>0.3</v>
@@ -16957,21 +17083,21 @@
         <v>0.7</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D117" s="7" t="n">
         <v>0.2</v>
@@ -16983,21 +17109,21 @@
         <v>0.35</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D118" s="7" t="n">
         <v>0.1</v>
@@ -17009,18 +17135,18 @@
         <v>0.5</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D119" s="7" t="n">
         <v>0.05</v>
@@ -17032,18 +17158,18 @@
         <v>0.15</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D120" s="7" t="n">
         <v>68</v>
@@ -17055,21 +17181,21 @@
         <v>80</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H120" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D121" s="7" t="n">
         <v>16</v>
@@ -17081,50 +17207,50 @@
         <v>20</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H121" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E122" s="7" t="n">
         <v>26</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H122" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E123" s="7" t="n">
         <v>0.13</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -17152,32 +17278,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B4" s="10" t="n">
         <f aca="false">u_bw_26</f>
@@ -17196,12 +17322,12 @@
         <v>0.25</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B5" s="10" t="n">
         <f aca="false">u_rb_26</f>
@@ -17220,12 +17346,12 @@
         <v>8.05</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B6" s="10" t="n">
         <f aca="false">u_ru_26</f>
@@ -17244,12 +17370,12 @@
         <v>2.3</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B7" s="10" t="n">
         <f aca="false">u_hp_26</f>
@@ -17268,12 +17394,12 @@
         <v>0</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B8" s="10" t="n">
         <f aca="false">u_amd_26</f>
@@ -17292,12 +17418,12 @@
         <v>2.3</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B9" s="10" t="n">
         <f aca="false">u_tpu_26</f>
@@ -17316,12 +17442,12 @@
         <v>8.05</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B10" s="10" t="n">
         <f aca="false">u_trn_26</f>
@@ -17340,12 +17466,12 @@
         <v>3.45</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B11" s="10" t="n">
         <f aca="false">u_oth_26</f>
@@ -17364,12 +17490,12 @@
         <v>5.75</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>323</v>
+      <c r="A12" s="4" t="s">
+        <v>324</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">SUM(B4:B11)</f>
@@ -17414,43 +17540,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>326</v>
+      <c r="A4" s="4" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>327</v>
+      <c r="A5" s="2" t="s">
+        <v>328</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C5" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_su_sw+Units!B5*c_VR_su_sw+Units!B6*c_RU_su_sw+Units!B7*c_HP_su_sw+Units!B8*c_AMD8_su_sw+Units!B9*c_TPU_su_sw+Units!B10*c_TRN_su_sw+Units!B11*c_ASIC_su_sw)/1000</f>
@@ -17470,11 +17596,11 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>328</v>
+      <c r="A6" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C6" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_su_ic+Units!B5*c_VR_su_ic+Units!B6*c_RU_su_ic+Units!B7*c_HP_su_ic+Units!B8*c_AMD8_su_ic+Units!B9*c_TPU_su_ic+Units!B10*c_TRN_su_ic+Units!B11*c_ASIC_su_ic)/1000</f>
@@ -17494,11 +17620,11 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>329</v>
+      <c r="A7" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C7" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_so_sw+Units!B5*c_VR_so_sw+Units!B6*c_RU_so_sw+Units!B7*c_HP_so_sw+Units!B8*c_AMD8_so_sw+Units!B9*c_TPU_so_sw+Units!B10*c_TRN_so_sw+Units!B11*c_ASIC_so_sw)/1000</f>
@@ -17518,11 +17644,11 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>330</v>
+      <c r="A8" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C8" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_so_opt+Units!B5*c_VR_so_opt+Units!B6*c_RU_so_opt+Units!B7*c_HP_so_opt+Units!B8*c_AMD8_so_opt+Units!B9*c_TPU_so_opt+Units!B10*c_TRN_so_opt+Units!B11*c_ASIC_so_opt)/1000</f>
@@ -17542,11 +17668,11 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>331</v>
+      <c r="A9" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_so_cu+Units!B5*c_VR_so_cu+Units!B6*c_RU_so_cu+Units!B7*c_HP_so_cu+Units!B8*c_AMD8_so_cu+Units!B9*c_TPU_so_cu+Units!B10*c_TRN_so_cu+Units!B11*c_ASIC_so_cu)/1000</f>
@@ -17566,11 +17692,11 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>332</v>
+      <c r="A10" s="3" t="s">
+        <v>333</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_nic+Units!B5*c_VR_nic+Units!B6*c_RU_nic+Units!B7*c_HP_nic+Units!B8*c_AMD8_nic+Units!B9*c_TPU_nic+Units!B10*c_TRN_nic+Units!B11*c_ASIC_nic)/1000</f>
@@ -17591,10 +17717,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">SUM(C5:C10)</f>
@@ -17614,11 +17740,11 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>334</v>
+      <c r="A12" s="3" t="s">
+        <v>335</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="12" t="n">
         <f aca="false">D11/C11-1</f>
@@ -17634,11 +17760,11 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>335</v>
+      <c r="A13" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="12" t="n">
         <f aca="false">(C5+C6)/C11</f>
@@ -17657,15 +17783,15 @@
         <v>0.279104336238518</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>337</v>
+      <c r="A14" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="12" t="n">
         <f aca="false">1-C13</f>
@@ -17685,16 +17811,16 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>338</v>
+      <c r="A16" s="4" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>339</v>
+      <c r="A17" s="3" t="s">
+        <v>340</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C17" s="11" t="n">
         <f aca="false">C5+C7</f>
@@ -17714,11 +17840,11 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>340</v>
+      <c r="A18" s="3" t="s">
+        <v>341</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C18" s="11" t="n">
         <f aca="false">C8+C6*suopt_26</f>
@@ -17738,11 +17864,11 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>341</v>
+      <c r="A19" s="3" t="s">
+        <v>342</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C19" s="11" t="n">
         <f aca="false">C8*cpo_26</f>
@@ -17762,11 +17888,11 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>342</v>
+      <c r="A20" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C20" s="11" t="n">
         <f aca="false">C18-C19</f>
@@ -17786,11 +17912,11 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>343</v>
+      <c r="A21" s="3" t="s">
+        <v>344</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C21" s="11" t="n">
         <f aca="false">C9+C6*(1-suopt_26)*su_cu</f>
@@ -17810,11 +17936,11 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>344</v>
+      <c r="A22" s="3" t="s">
+        <v>345</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C22" s="11" t="n">
         <f aca="false">C6*(1-suopt_26)*(1-su_cu)</f>
@@ -17834,11 +17960,11 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>345</v>
+      <c r="A23" s="3" t="s">
+        <v>346</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C23" s="11" t="n">
         <f aca="false">C10</f>
@@ -17858,11 +17984,11 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>346</v>
+      <c r="A24" s="3" t="s">
+        <v>347</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C24" s="13" t="n">
         <f aca="false">C17+C18+C21+C22+C23-C11</f>
@@ -17882,16 +18008,16 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>347</v>
+      <c r="A26" s="4" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>348</v>
+      <c r="A27" s="2" t="s">
+        <v>349</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C27" s="11" t="n">
         <f aca="false">(Units!B4*it_GB+Units!B5*it_VR+Units!B6*it_RU+Units!B7*it_HP+Units!B8*it_AMD8+Units!B9*it_TPU+Units!B10*it_TRN+Units!B11*it_ASIC)</f>
@@ -17910,15 +18036,15 @@
         <v>2260.39027777778</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>350</v>
+      <c r="A28" s="3" t="s">
+        <v>351</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C28" s="14" t="n">
         <f aca="false">C11/C27</f>
@@ -17937,15 +18063,15 @@
         <v>0.170477418783998</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>352</v>
+      <c r="A29" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" s="14" t="n">
         <f aca="false">((Units!B4*c_GB_su_sw+Units!B5*c_VR_su_sw+Units!B6*c_RU_su_sw+Units!B7*c_HP_su_sw)/1000+(Units!B4*c_GB_su_ic+Units!B5*c_VR_su_ic+Units!B6*c_RU_su_ic+Units!B7*c_HP_su_ic)/1000+(Units!B4*c_GB_so_sw+Units!B5*c_VR_so_sw+Units!B6*c_RU_so_sw+Units!B7*c_HP_so_sw)/1000+(Units!B4*c_GB_so_opt+Units!B5*c_VR_so_opt+Units!B6*c_RU_so_opt+Units!B7*c_HP_so_opt)/1000+(Units!B4*c_GB_so_cu+Units!B5*c_VR_so_cu+Units!B6*c_RU_so_cu+Units!B7*c_HP_so_cu)/1000+(Units!B4*c_GB_nic+Units!B5*c_VR_nic+Units!B6*c_RU_nic+Units!B7*c_HP_nic)/1000)/(Units!B4*it_GB+Units!B5*it_VR+Units!B6*it_RU+Units!B7*it_HP)</f>
@@ -17965,16 +18091,16 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>353</v>
+      <c r="A31" s="4" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
-        <v>354</v>
+      <c r="A32" s="2" t="s">
+        <v>355</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C32" s="11" t="n">
         <f aca="false">(Units!B4*c_GB_su_sw+Units!B5*c_VR_su_sw+Units!B6*c_RU_su_sw+Units!B7*c_HP_su_sw)/1000+nv_su_ic*(Units!B4*c_GB_su_ic+Units!B5*c_VR_su_ic+Units!B6*c_RU_su_ic+Units!B7*c_HP_su_ic)/1000+nv_so_sw*(Units!B4*c_GB_so_sw+Units!B5*c_VR_so_sw+Units!B6*c_RU_so_sw+Units!B7*c_HP_so_sw)/1000+(Units!B4*c_GB_nic+Units!B5*c_VR_nic+Units!B6*c_RU_nic+Units!B7*c_HP_nic)/1000+nv_opt*(Units!B4*c_GB_so_opt+Units!B5*c_VR_so_opt+Units!B6*c_RU_so_opt+Units!B7*c_HP_so_opt)/1000</f>
@@ -17994,11 +18120,11 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>355</v>
+      <c r="A33" s="3" t="s">
+        <v>356</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C33" s="11" t="n">
         <f aca="false">rep_nv26</f>
@@ -18006,11 +18132,11 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>356</v>
+      <c r="A34" s="3" t="s">
+        <v>357</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C34" s="12" t="n">
         <f aca="false">C32/C33-1</f>
@@ -18018,11 +18144,11 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>357</v>
+      <c r="A35" s="2" t="s">
+        <v>358</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C35" s="11" t="n">
         <f aca="false">avgo_su*(Units!B8*c_AMD8_su_sw+Units!B9*c_TPU_su_sw+Units!B10*c_TRN_su_sw+Units!B11*c_ASIC_su_sw)/1000+avgo_so*((1-nv_so_sw)*(Units!B4*c_GB_so_sw+Units!B5*c_VR_so_sw+Units!B6*c_RU_so_sw+Units!B7*c_HP_so_sw)/1000+(Units!B8*c_AMD8_so_sw+Units!B9*c_TPU_so_sw+Units!B10*c_TRN_so_sw+Units!B11*c_ASIC_so_sw)/1000)+avgo_nic*(Units!B8*c_AMD8_nic+Units!B9*c_TPU_nic+Units!B10*c_TRN_nic+Units!B11*c_ASIC_nic)/1000+avgo_opt*C18</f>
@@ -18042,11 +18168,11 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
-        <v>358</v>
+      <c r="A36" s="3" t="s">
+        <v>359</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C36" s="11" t="n">
         <f aca="false">rep_avgo26</f>
@@ -18054,11 +18180,11 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
-        <v>356</v>
+      <c r="A37" s="3" t="s">
+        <v>357</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C37" s="12" t="n">
         <f aca="false">C35/C36-1</f>
@@ -18066,11 +18192,11 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>359</v>
+      <c r="A38" s="2" t="s">
+        <v>360</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C38" s="12" t="n">
         <f aca="false">(C32+C35)/C11</f>
@@ -18089,15 +18215,15 @@
         <v>0.506383309004517</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
-        <v>361</v>
+      <c r="A39" s="3" t="s">
+        <v>362</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C39" s="11" t="n">
         <f aca="false">C18</f>
@@ -18108,15 +18234,15 @@
         <v>26</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
-        <v>356</v>
+      <c r="A40" s="3" t="s">
+        <v>357</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C40" s="12" t="n">
         <f aca="false">C39/D39-1</f>
@@ -18148,26 +18274,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">Mkt!D11</f>
@@ -18180,7 +18306,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">Mkt!D11-0.3*u_rb_27*(c_VR_su_sw+c_VR_su_ic+c_VR_so_sw+c_VR_so_opt+c_VR_so_cu+c_VR_nic)/1000</f>
@@ -18191,12 +18317,12 @@
         <v>-0.175948810464954</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">Mkt!D11+0.3*u_rb_27*(c_VR_su_sw+c_VR_su_ic+c_VR_so_sw+c_VR_so_opt+c_VR_so_cu+c_VR_nic)/1000</f>
@@ -18209,7 +18335,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">Mkt!D11-0.2*u_rb_27*(c_VR_su_sw+c_VR_su_ic+c_VR_so_sw+c_VR_so_opt+c_VR_so_cu+c_VR_nic)/1000</f>
@@ -18222,7 +18348,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">Mkt!D11+0.2*u_rb_27*(c_VR_su_sw+c_VR_su_ic+c_VR_so_sw+c_VR_so_opt+c_VR_so_cu+c_VR_nic)/1000</f>
@@ -18235,7 +18361,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">Mkt!D11+(Units!C9*(c_TPU_su_sw+c_TPU_su_ic+c_TPU_so_sw+c_TPU_so_opt+c_TPU_so_cu+c_TPU_nic)+Units!C10*(c_TRN_su_sw+c_TRN_su_ic+c_TRN_so_sw+c_TRN_so_opt+c_TRN_so_cu+c_TRN_nic)+Units!C11*(c_ASIC_su_sw+c_ASIC_su_ic+c_ASIC_so_sw+c_ASIC_so_opt+c_ASIC_so_cu+c_ASIC_nic))/1000</f>
@@ -18246,7 +18372,7 @@
         <v>0.189775770523822</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -18273,112 +18399,112 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>374</v>
+      <c r="A1" s="4" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>377</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
